--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N77_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N77_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.65547301015538</v>
+        <v>7.41901436415025</v>
       </c>
       <c r="D2" t="n">
-        <v>45.14776658329318</v>
+        <v>7.336512069785143</v>
       </c>
       <c r="E2" t="n">
-        <v>11.28003506181956</v>
+        <v>1.833005697545679</v>
       </c>
       <c r="F2" t="n">
-        <v>11.03702689761319</v>
+        <v>1.793516870862144</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.67394621121329</v>
+        <v>7.09701625932216</v>
       </c>
       <c r="D3" t="n">
-        <v>43.11258671390733</v>
+        <v>7.005795341009942</v>
       </c>
       <c r="E3" t="n">
-        <v>11.28003506181956</v>
+        <v>1.833005697545679</v>
       </c>
       <c r="F3" t="n">
-        <v>11.03702689761319</v>
+        <v>1.793516870862144</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.58576738030703</v>
+        <v>4.157687199299892</v>
       </c>
       <c r="D4" t="n">
-        <v>26.37577260661266</v>
+        <v>4.286063048574557</v>
       </c>
       <c r="E4" t="n">
-        <v>11.28003506181956</v>
+        <v>1.833005697545679</v>
       </c>
       <c r="F4" t="n">
-        <v>11.03702689761319</v>
+        <v>1.793516870862144</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.39319303231309</v>
+        <v>4.938893867750878</v>
       </c>
       <c r="D5" t="n">
-        <v>29.93040870928058</v>
+        <v>4.863691415258094</v>
       </c>
       <c r="E5" t="n">
-        <v>11.28003506181956</v>
+        <v>1.833005697545679</v>
       </c>
       <c r="F5" t="n">
-        <v>11.03702689761319</v>
+        <v>1.793516870862144</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.34041192903648</v>
+        <v>2.817816938468428</v>
       </c>
       <c r="D6" t="n">
-        <v>17.35156919452546</v>
+        <v>2.819629994110388</v>
       </c>
       <c r="E6" t="n">
-        <v>11.28003506181956</v>
+        <v>1.833005697545679</v>
       </c>
       <c r="F6" t="n">
-        <v>11.03702689761319</v>
+        <v>1.793516870862144</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.27790519605362</v>
+        <v>7.032659594358714</v>
       </c>
       <c r="D7" t="n">
-        <v>42.62643413643676</v>
+        <v>6.926795547170975</v>
       </c>
       <c r="E7" t="n">
-        <v>11.28003506181956</v>
+        <v>1.833005697545679</v>
       </c>
       <c r="F7" t="n">
-        <v>11.03702689761319</v>
+        <v>1.793516870862144</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.47122380931523</v>
+        <v>5.601573869013724</v>
       </c>
       <c r="D8" t="n">
-        <v>34.56849422690125</v>
+        <v>5.617380311871454</v>
       </c>
       <c r="E8" t="n">
-        <v>11.28003506181956</v>
+        <v>1.833005697545679</v>
       </c>
       <c r="F8" t="n">
-        <v>11.03702689761319</v>
+        <v>1.793516870862144</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.23605965589981</v>
+        <v>3.613359694083719</v>
       </c>
       <c r="D9" t="n">
-        <v>22.30882522957952</v>
+        <v>3.625184099806671</v>
       </c>
       <c r="E9" t="n">
-        <v>11.28003506181956</v>
+        <v>1.833005697545679</v>
       </c>
       <c r="F9" t="n">
-        <v>11.03702689761319</v>
+        <v>1.793516870862144</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.31152044189371</v>
+        <v>5.575622071807729</v>
       </c>
       <c r="D10" t="n">
-        <v>34.48301919212985</v>
+        <v>5.6034906187211</v>
       </c>
       <c r="E10" t="n">
-        <v>11.28003506181956</v>
+        <v>1.833005697545679</v>
       </c>
       <c r="F10" t="n">
-        <v>11.03702689761319</v>
+        <v>1.793516870862144</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>7.793828885640486</v>
+        <v>1.266497193916579</v>
       </c>
       <c r="D11" t="n">
-        <v>8.06692512570498</v>
+        <v>1.310875332927059</v>
       </c>
       <c r="E11" t="n">
-        <v>11.28003506181956</v>
+        <v>1.833005697545679</v>
       </c>
       <c r="F11" t="n">
-        <v>11.03702689761319</v>
+        <v>1.793516870862144</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>25.59671894747702</v>
+        <v>4.159466828965015</v>
       </c>
       <c r="D12" t="n">
-        <v>25.00561949328021</v>
+        <v>4.063413167658035</v>
       </c>
       <c r="E12" t="n">
-        <v>11.28003506181956</v>
+        <v>1.833005697545679</v>
       </c>
       <c r="F12" t="n">
-        <v>11.03702689761319</v>
+        <v>1.793516870862144</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
